--- a/outputs/7665.xlsx
+++ b/outputs/7665.xlsx
@@ -1,68 +1,84 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+  <fileVersion appName="Calc" lowestEdited="4"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$H$1:$H$18</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Sheet1!$H$1:$H$18</definedName>
   </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <extLst>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
+    </ext>
+  </extLst>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="1">
+  <si>
+    <t xml:space="preserve">Number List</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.0000"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
+    <numFmt numFmtId="166" formatCode="0"/>
   </numFmts>
   <fonts count="6">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
+      <family val="0"/>
       <charset val="134"/>
-      <family val="0"/>
-      <color theme="1"/>
-      <sz val="11"/>
     </font>
     <font>
+      <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-      <sz val="10"/>
     </font>
     <font>
+      <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-      <sz val="10"/>
     </font>
     <font>
+      <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-      <sz val="10"/>
     </font>
     <font>
+      <b val="true"/>
+      <sz val="11"/>
       <name val="宋体"/>
+      <family val="0"/>
       <charset val="134"/>
-      <family val="0"/>
-      <b val="1"/>
-      <sz val="11"/>
     </font>
     <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
+      <family val="0"/>
       <charset val="134"/>
-      <family val="0"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
     </font>
   </fonts>
   <fills count="4">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -81,14 +97,14 @@
     </fill>
   </fills>
   <borders count="2">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left style="thin"/>
       <right style="thin"/>
       <top style="thin"/>
@@ -96,68 +112,72 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
+  <cellStyleXfs count="20">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="15">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
+  <cellXfs count="8">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="2" builtinId="6"/>
-    <cellStyle name="Currency" xfId="3" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
-    <cellStyle name="Percent" xfId="5" builtinId="5"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
   <dxfs count="2">
     <dxf>
@@ -239,6 +259,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme 2007 - 2010">
   <a:themeElements>
@@ -415,155 +439,149 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="H1:V20"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.8359375" defaultRowHeight="16.5" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr defaultColWidth="8.8359375" defaultRowHeight="16.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col width="4.67" customWidth="1" style="7" min="1" max="7"/>
-    <col width="16" customWidth="1" style="7" min="8" max="8"/>
-    <col width="4.67" customWidth="1" style="7" min="9" max="16"/>
-    <col width="16.34" customWidth="1" style="7" min="17" max="17"/>
-    <col width="4.67" customWidth="1" style="7" min="18" max="23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="1" style="1" width="4.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="9" style="1" width="4.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="16.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="18" style="1" width="4.67"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" customHeight="1" s="8">
-      <c r="H1" s="9" t="inlineStr">
-        <is>
-          <t>Number List</t>
-        </is>
-      </c>
-      <c r="Q1" s="10" t="inlineStr">
-        <is>
-          <t>Number List</t>
-        </is>
-      </c>
-      <c r="R1" s="11" t="n"/>
-      <c r="S1" s="11" t="n"/>
-      <c r="T1" s="11" t="n"/>
-      <c r="U1" s="11" t="n"/>
-      <c r="V1" s="11" t="n"/>
-    </row>
-    <row r="2" ht="16.5" customHeight="1" s="8">
-      <c r="H2" s="12" t="n">
+    <row r="1" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="R1" s="4"/>
+      <c r="S1" s="4"/>
+      <c r="T1" s="4"/>
+      <c r="U1" s="4"/>
+      <c r="V1" s="4"/>
+    </row>
+    <row r="2" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H2" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="Q2" s="11">
-        <f>SMALL(_xlfn.UNIQUE(H2:H18),COLUMN()-16)</f>
-        <v/>
-      </c>
-      <c r="R2" s="11">
-        <f>SMALL(_xlfn.UNIQUE(H2:H18),COLUMN()-16)</f>
-        <v/>
-      </c>
-      <c r="S2" s="11">
-        <f>SMALL(_xlfn.UNIQUE(H2:H18),COLUMN()-16)</f>
-        <v/>
-      </c>
-      <c r="T2" s="11">
-        <f>SMALL(_xlfn.UNIQUE(H2:H18),COLUMN()-16)</f>
-        <v/>
-      </c>
-      <c r="U2" s="11">
-        <f>SMALL(_xlfn.UNIQUE(H2:H18),COLUMN()-16)</f>
-        <v/>
-      </c>
-      <c r="V2" s="11">
-        <f>SMALL(_xlfn.UNIQUE(H2:H18),COLUMN()-16)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="3" ht="16.5" customHeight="1" s="8">
-      <c r="H3" s="12" t="n">
+      <c r="Q2" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="R2" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="S2" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="T2" s="4" t="n">
         <v>44</v>
       </c>
-    </row>
-    <row r="4" ht="16.5" customHeight="1" s="8">
-      <c r="H4" s="12" t="n">
+      <c r="U2" s="4" t="n">
+        <v>66</v>
+      </c>
+      <c r="V2" s="4" t="n">
         <v>77</v>
       </c>
-      <c r="Q4" s="13" t="n"/>
-    </row>
-    <row r="5" ht="16.5" customHeight="1" s="8">
-      <c r="H5" s="12" t="n">
+    </row>
+    <row r="3" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H3" s="5" t="n">
         <v>44</v>
       </c>
     </row>
-    <row r="6" ht="16.5" customHeight="1" s="8">
-      <c r="H6" s="12" t="n">
+    <row r="4" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H4" s="5" t="n">
+        <v>77</v>
+      </c>
+      <c r="Q4" s="6"/>
+    </row>
+    <row r="5" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H5" s="5" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H6" s="5" t="n">
         <v>33</v>
       </c>
     </row>
-    <row r="7" ht="16.5" customHeight="1" s="8">
-      <c r="H7" s="12" t="n">
+    <row r="7" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H7" s="5" t="n">
         <v>33</v>
       </c>
     </row>
-    <row r="8" ht="16.5" customHeight="1" s="8">
-      <c r="H8" s="12" t="n">
+    <row r="8" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H8" s="5" t="n">
         <v>33</v>
       </c>
     </row>
-    <row r="9" ht="16.5" customHeight="1" s="8">
-      <c r="H9" s="12" t="n">
+    <row r="9" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H9" s="5" t="n">
         <v>77</v>
       </c>
     </row>
-    <row r="10" ht="16.5" customHeight="1" s="8">
-      <c r="H10" s="12" t="n">
+    <row r="10" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H10" s="5" t="n">
         <v>44</v>
       </c>
     </row>
-    <row r="11" ht="16.5" customHeight="1" s="8">
-      <c r="H11" s="12" t="n">
+    <row r="11" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H11" s="5" t="n">
         <v>66</v>
       </c>
     </row>
-    <row r="12" ht="16.5" customHeight="1" s="8">
-      <c r="H12" s="12" t="n">
+    <row r="12" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H12" s="5" t="n">
         <v>22</v>
       </c>
     </row>
-    <row r="13" ht="16.5" customHeight="1" s="8">
-      <c r="H13" s="12" t="n">
+    <row r="13" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H13" s="5" t="n">
         <v>22</v>
       </c>
     </row>
-    <row r="14" ht="16.5" customHeight="1" s="8">
-      <c r="H14" s="12" t="n">
+    <row r="14" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H14" s="5" t="n">
         <v>22</v>
       </c>
     </row>
-    <row r="15" ht="16.5" customHeight="1" s="8">
-      <c r="H15" s="12" t="n">
+    <row r="15" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H15" s="5" t="n">
         <v>33</v>
       </c>
     </row>
-    <row r="16" ht="16.5" customHeight="1" s="8">
-      <c r="H16" s="12" t="n">
+    <row r="16" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H16" s="5" t="n">
         <v>44</v>
       </c>
     </row>
-    <row r="17" ht="16.5" customHeight="1" s="8">
-      <c r="H17" s="12" t="n">
+    <row r="17" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H17" s="5" t="n">
         <v>44</v>
       </c>
     </row>
-    <row r="18" ht="16.5" customHeight="1" s="8">
-      <c r="H18" s="12" t="n">
+    <row r="18" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H18" s="5" t="n">
         <v>11</v>
       </c>
     </row>
-    <row r="20" ht="16.5" customHeight="1" s="8">
-      <c r="H20" s="14" t="n"/>
+    <row r="20" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H20" s="7"/>
     </row>
   </sheetData>
   <autoFilter ref="H1:H18"/>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>